--- a/02_加值成品/生物/生物3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-3 淋巴與免疫　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物3-3 淋巴與免疫　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>回收組織液的系統是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>皮膚與黏膜</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>第一道屏障</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>淋巴系統</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>回收</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>免疫的第一道防線是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>病毒株會變異</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>抗體</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>皮膚與黏膜</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>屏障</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>能吞噬病原的血球是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>白血球</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>過度反應</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>易受感染</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>吞噬</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>對抗特定病原的物質是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>抗體</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>病原體</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>預防</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>專一</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>使身體預先免疫的是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>產生免疫記憶</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>協助防禦</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>疫苗</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>免疫發炎反應</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>預防</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>抵抗病原體的機制稱？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>免疫</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>皮膚與黏膜</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>抗體</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>產生免疫記憶</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>防禦</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>淋巴結的作用是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>協助防禦</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>免疫發炎反應</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>淋巴球</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>過濾</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>產生抗體的細胞是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>免疫發炎反應</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>淋巴球</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>免疫</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>免疫系統對抗的對象是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>產生免疫記憶</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>過度反應</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>病原體</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>防禦</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>接種疫苗屬於預防還治療？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>免疫</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>預防</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>產生免疫記憶</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>預防</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-3 淋巴與免疫　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物3-3 淋巴與免疫　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>抗體具有什麼特性？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>專一性</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>產生免疫記憶</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>協助防禦</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>對特定</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>疫苗含什麼成分？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>減弱或無害病原</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>回收組織液並過濾病原協助免疫</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>免疫系統記住病原能快速反應</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>抗原</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>皮膚在免疫的角色？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>第一道屏障</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>腫大</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>阻擋</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>感染時淋巴結可能會？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>腫大</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>抵抗</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>打疫苗後身體會？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>抗體</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>產生免疫記憶</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>記憶</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>白血球增加常因？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>抗體</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>對抗感染</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>防禦</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>抗體與抗原的關係？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>減弱或無害病原</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>免疫系統記住病原能快速反應</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>抗體對抗特定抗原</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>專一</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>傷口紅腫是什麼反應？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>淋巴系統</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>免疫發炎反應</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>反應</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>第一次感染後身體會留下？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>專一性</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>免疫記憶</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>記憶</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>過敏是免疫系統的什麼反應？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>白血球</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>協助防禦</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>腫大</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>過度反應</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>免疫</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物3-3 淋巴與免疫　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物3-3 淋巴與免疫　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明人體對抗病原的多道防線？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>快速產生大量抗體</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>抗體對抗特定抗原</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>免疫系統記住病原能快速反應</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>防線</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>疫苗如何使人預先獲得免疫力？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>疫苗預防、藥物多為治療</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>抗體對抗特定抗原</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>引入無害抗原使身體產生抗體與記憶</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何得過某病後常不再得(免疫記憶)？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>減弱或無害病原</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>抗體對抗特定抗原</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>免疫系統記住病原能快速反應</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>記憶</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>抗體專一性的意義？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>免疫系統記住病原能快速反應</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>針對特定病原精準防禦</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>疫苗預防、藥物多為治療</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>專一</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>淋巴系統如何與循環系統協同防禦？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>減弱或無害病原</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>回收組織液並過濾病原協助免疫</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>疫苗預防、藥物多為治療</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>協同</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>免疫力低下對健康的影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>易受感染</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>免疫記憶</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>對抗感染</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>皮膚與黏膜</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>免疫</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>疫苗與藥物治療的差別？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>減弱或無害病原</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>免疫系統記住病原能快速反應</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>疫苗預防、藥物多為治療</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>發炎紅腫熱痛的生理意義？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>皮膚黏膜阻擋、白血球吞噬、淋巴球產抗體</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>抗體對抗特定抗原</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>減弱或無害病原</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>免疫細胞集中對抗病原</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>反應</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何流感疫苗需要每年接種？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>皮膚與黏膜</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>病毒株會變異</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>病原體</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>疫苗</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>變異</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>免疫記憶如何讓二次感染較快康復？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>減弱或無害病原</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>引入無害抗原使身體產生抗體與記憶</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>快速產生大量抗體</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>回收組織液並過濾病原協助免疫</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>記憶</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>回收</t>
+          <t>回收：淋巴系統負責回收滲出到組織間的液體，並協助身體防禦</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>屏障</t>
+          <t>屏障：皮膚和黏膜是身體對抗病原體的第一道防線，能直接阻擋病原侵入</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>吞噬</t>
+          <t>吞噬：白血球能主動吞噬並消滅侵入體內的病原體</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>專一</t>
+          <t>專一：抗體是身體針對特定病原體所產生的物質，能專一地對抗它</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>預防</t>
+          <t>預防：疫苗讓身體提前接觸無害的病原成分，預先產生免疫力來預防疾病</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>防禦</t>
+          <t>防禦：身體抵抗病原體入侵的整套機制稱為免疫</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>過濾</t>
+          <t>過濾：淋巴結能過濾淋巴液中的病原體，協助身體防禦</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>免疫</t>
+          <t>免疫：淋巴球是白血球的一種，能針對特定病原體產生抗體</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>防禦</t>
+          <t>防禦：免疫系統主要負責辨識並對抗入侵體內的病原體，如細菌、病毒等</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>預防</t>
+          <t>預防：疫苗是在還沒生病前，先讓身體產生免疫記憶，用來預防未來感染，屬於預防措施</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>對特定</t>
+          <t>對特定：抗體只能對抗和它相對應的特定病原體，不能對抗所有病原</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>抗原</t>
+          <t>抗原：疫苗裡含有減弱或無害的病原成分，用來刺激身體產生免疫力</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>阻擋</t>
+          <t>阻擋：皮膚是身體對外的屏障，能阻擋大多數病原體進入體內</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>抵抗</t>
+          <t>抵抗：感染時淋巴結常因淋巴球增生而腫大，代表正在抵抗感染</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>記憶</t>
+          <t>記憶：接種疫苗後身體會記住這種病原的特徵，之後接觸能更快產生抗體</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>防禦</t>
+          <t>防禦：白血球數量增加通常是身體正在對抗細菌或病毒等感染</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>專一</t>
+          <t>專一：抗體會專一地辨認並對抗與它相對應的抗原</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>反應</t>
+          <t>反應：傷口紅腫是免疫系統派出白血球對抗病原時引發的發炎反應</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>記憶</t>
+          <t>記憶：身體第一次接觸某種病原體後，免疫系統會保留對它的記憶，稱為免疫記憶，方便下次更快反應</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>免疫</t>
+          <t>免疫：過敏是免疫系統對原本無害的物質（如花粉）產生過度激烈的防禦反應，反而造成身體不適</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>防線</t>
+          <t>防線：先靠皮膚黏膜阻擋病原，若突破則白血球吞噬，最後淋巴球產抗體精準對抗</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：疫苗讓身體接觸無害的病原成分，促使身體產生抗體並留下免疫記憶</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>記憶</t>
+          <t>記憶：免疫系統已記住病原的特徵，下次接觸時能更快產生抗體消滅它</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>專一</t>
+          <t>專一：抗體只針對特定病原發揮作用，能精準有效地消滅入侵的病原體</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>協同</t>
+          <t>協同：淋巴系統回收組織液的同時也過濾其中的病原體，配合免疫系統防禦</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>免疫</t>
+          <t>免疫：免疫力低下時身體抵抗病原的能力變弱，比較容易生病</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：疫苗的作用是預先預防疾病發生，藥物則多用於生病後的治療</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>反應</t>
+          <t>反應：紅腫熱痛代表免疫細胞正大量集中到受傷或感染部位對抗病原</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>變異</t>
+          <t>變異：流感病毒容易產生變異，每年流行的病毒株可能不同，先前的免疫記憶不一定能完全對抗新病毒株，所以需要每年接種更新的疫苗</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>記憶</t>
+          <t>記憶：由於身體已經留有對該病原體的免疫記憶，再次遇到同一種病原體時，能更快速地大量產生抗體加以清除，因此二次感染通常恢復得比較快</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物3-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物3-3_三種難度測驗卷.xlsx
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>皮膚與黏膜</t>
+          <t>淋巴系統</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>抗體</t>
+          <t>淋巴球</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>產生免疫記憶</t>
+          <t>白血球</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>抗體</t>
+          <t>預防</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>疫苗</t>
+          <t>淋巴球</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>淋巴系統</t>
+          <t>免疫記憶</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>白血球</t>
+          <t>淋巴球</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>專一性</t>
+          <t>協助防禦</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1359,22 +1359,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>專一性</t>
+          <t>淋巴系統</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>淋巴球</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>免疫記憶</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>疫苗</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>免疫記憶</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>白血球</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
